--- a/business/bids/ETABLIX-PROJECT-FINANCE-TABLE.xlsx
+++ b/business/bids/ETABLIX-PROJECT-FINANCE-TABLE.xlsx
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Labour Costs  (£) </t>
   </si>
   <si>
-    <t>Managing Director, 24 days at £550/day across October 2026 to March 2027 — pack ingestion, engine configuration, running three demonstrations, buyer sessions and write-up. Source: ETABLIX, in kind, not charged to the grant.</t>
+    <t>Managing Director, 42 days at £550/day across October 2026 to March 2027, in two parts. Demonstration delivery, 24 days: pack ingestion, engine configuration, running three demonstrations, buyer sessions and write-up. Programme participation, 18 days: coaching sessions, customer days and investor readiness work. Source: ETABLIX, in kind, not charged to the grant and tracked for the programme's records.</t>
   </si>
   <si>
     <t>Facilities made available (ie. lab space etc.) (£)</t>
@@ -251,7 +251,7 @@
     <t>[Your name] — Managing Director, ETABLIX</t>
   </si>
   <si>
-    <t>24 days at £550/day, contributed as match funding and NOT charged to this grant. Days: pack ingestion and engine configuration (8), running three demonstrations and preparing the comparisons (9), buyer sessions and travel (4), write-up and liaison with the independent verifier (3).</t>
+    <t>42 days at £550/day, contributed as match funding and NOT charged to this grant. Demonstration delivery, 24 days: pack ingestion and engine configuration (8), running three demonstrations and preparing the comparisons (9), buyer sessions and travel (4), write-up and liaison with the independent verifier (3). Programme participation, 18 days at 3 per month: coaching, customer days and investor readiness work.</t>
   </si>
   <si>
     <t>Consultancy Costs</t>
@@ -2273,7 +2273,7 @@
         <v>34</v>
       </c>
       <c r="C25" s="53">
-        <v>13200</v>
+        <v>23100</v>
       </c>
       <c r="D25" s="54" t="s">
         <v>35</v>
